--- a/datasheet.xlsx
+++ b/datasheet.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42872E7E-8194-4BE9-8472-8387A2CFB560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC06F719-CE51-4023-B540-308AC5370686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="login" sheetId="1" r:id="rId1"/>
-    <sheet name="usercreation" sheetId="2" r:id="rId2"/>
+    <sheet name="userCreation" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="67">
   <si>
     <t>Admin</t>
   </si>
@@ -45,18 +45,18 @@
     <t>admin1234</t>
   </si>
   <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Middle Name</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
     <t>EmployeeId</t>
   </si>
   <si>
-    <t>First Name</t>
-  </si>
-  <si>
-    <t>Middle Name</t>
-  </si>
-  <si>
-    <t>LastName</t>
-  </si>
-  <si>
     <t xml:space="preserve">Toggle On </t>
   </si>
   <si>
@@ -70,14 +70,169 @@
   </si>
   <si>
     <t>Upload image</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Doe</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>John.doe123</t>
+  </si>
+  <si>
+    <t>Enabled</t>
+  </si>
+  <si>
+    <t>Manju@1234</t>
+  </si>
+  <si>
+    <t>testdata/test1.jpg</t>
+  </si>
+  <si>
+    <t>S.No</t>
+  </si>
+  <si>
+    <t>ScenarioType</t>
+  </si>
+  <si>
+    <t>ExecuteFlag</t>
+  </si>
+  <si>
+    <t>Test case status</t>
+  </si>
+  <si>
+    <t>Successfully Saved</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>Steve</t>
+  </si>
+  <si>
+    <t>Peter</t>
+  </si>
+  <si>
+    <t>James</t>
+  </si>
+  <si>
+    <t>Parker</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Negative</t>
+  </si>
+  <si>
+    <t>Required</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>Lee</t>
+  </si>
+  <si>
+    <t>Already Exists</t>
+  </si>
+  <si>
+    <t>Harry</t>
+  </si>
+  <si>
+    <t>Potter</t>
+  </si>
+  <si>
+    <t>Harry123</t>
+  </si>
+  <si>
+    <t>Test@1234</t>
+  </si>
+  <si>
+    <t>Passwords Do Not Match</t>
+  </si>
+  <si>
+    <t>Robert</t>
+  </si>
+  <si>
+    <t>Downey</t>
+  </si>
+  <si>
+    <t>Robert123</t>
+  </si>
+  <si>
+    <t>Password Must Meet Complexity Requirements</t>
+  </si>
+  <si>
+    <t>Clark</t>
+  </si>
+  <si>
+    <t>Kent</t>
+  </si>
+  <si>
+    <t>Superman</t>
+  </si>
+  <si>
+    <t>EMP1001</t>
+  </si>
+  <si>
+    <t>Clark001</t>
+  </si>
+  <si>
+    <t>Disabled</t>
+  </si>
+  <si>
+    <t>Bruce</t>
+  </si>
+  <si>
+    <t>Wayne</t>
+  </si>
+  <si>
+    <t>Batman</t>
+  </si>
+  <si>
+    <t>Employee Id Already Exists</t>
+  </si>
+  <si>
+    <t>Tony</t>
+  </si>
+  <si>
+    <t>Stark</t>
+  </si>
+  <si>
+    <t>Ironman</t>
+  </si>
+  <si>
+    <t>Tony@123</t>
+  </si>
+  <si>
+    <t>testdata/test.pdf</t>
+  </si>
+  <si>
+    <t>Invalid File Type</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -111,9 +266,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -464,50 +623,467 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16313A00-36E6-4ECF-BA1E-C9D31747B485}">
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:P11"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="40.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="2">
+        <v>123</v>
+      </c>
+      <c r="L8" s="2">
+        <v>123</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="E1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" t="s">
-        <v>17</v>
+      <c r="B10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/datasheet.xlsx
+++ b/datasheet.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC06F719-CE51-4023-B540-308AC5370686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="login" sheetId="1" r:id="rId1"/>
-    <sheet name="userCreation" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="login" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="userCreation" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="74">
   <si>
     <t>Admin</t>
   </si>
@@ -45,10 +44,19 @@
     <t>admin1234</t>
   </si>
   <si>
-    <t>First Name</t>
-  </si>
-  <si>
-    <t>Middle Name</t>
+    <t>S.No</t>
+  </si>
+  <si>
+    <t>ScenarioType</t>
+  </si>
+  <si>
+    <t>ExecuteFlag</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>MiddleName</t>
   </si>
   <si>
     <t>LastName</t>
@@ -57,7 +65,7 @@
     <t>EmployeeId</t>
   </si>
   <si>
-    <t xml:space="preserve">Toggle On </t>
+    <t>ToggleOn</t>
   </si>
   <si>
     <t>Username</t>
@@ -66,21 +74,30 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Confirm Password</t>
+    <t>ConfirmPassword</t>
   </si>
   <si>
     <t>Upload image</t>
   </si>
   <si>
+    <t>Test case status</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>John</t>
   </si>
   <si>
+    <t>Steve</t>
+  </si>
+  <si>
     <t>Doe</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>John.doe123</t>
   </si>
   <si>
@@ -93,25 +110,15 @@
     <t>testdata/test1.jpg</t>
   </si>
   <si>
-    <t>S.No</t>
-  </si>
-  <si>
-    <t>ScenarioType</t>
-  </si>
-  <si>
-    <t>ExecuteFlag</t>
-  </si>
-  <si>
-    <t>Test case status</t>
-  </si>
-  <si>
     <t>Successfully Saved</t>
   </si>
   <si>
-    <t>Positive</t>
-  </si>
-  <si>
-    <t>Steve</t>
+    <t xml:space="preserve">[2mexpect([22m[31mreceived[39m[2m).[22mtoContain[2m([22m[32mexpected[39m[2m) // indexOf[22m
+Expected substring: [32m"Successfully Saved"[39m
+Received string:    [31m"something went wrong"[39m</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
   <si>
     <t>Peter</t>
@@ -123,7 +130,7 @@
     <t>Parker</t>
   </si>
   <si>
-    <t>No</t>
+    <t>No success toast or validation message found</t>
   </si>
   <si>
     <t>Negative</t>
@@ -141,7 +148,7 @@
     <t>Lee</t>
   </si>
   <si>
-    <t>Already Exists</t>
+    <t>locator.count: Target page, context or browser has been closed</t>
   </si>
   <si>
     <t>Harry</t>
@@ -153,10 +160,13 @@
     <t>Harry123</t>
   </si>
   <si>
-    <t>Test@1234</t>
-  </si>
-  <si>
-    <t>Passwords Do Not Match</t>
+    <t>Abc@1234</t>
+  </si>
+  <si>
+    <t>Bca@1234</t>
+  </si>
+  <si>
+    <t>Passwords do not match</t>
   </si>
   <si>
     <t>Robert</t>
@@ -168,7 +178,20 @@
     <t>Robert123</t>
   </si>
   <si>
-    <t>Password Must Meet Complexity Requirements</t>
+    <t>Abc</t>
+  </si>
+  <si>
+    <t>bca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Should have at least 7 characters,
+Passwords do not match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[2mexpect([22m[31mreceived[39m[2m).[22mtoContain[2m([22m[32mexpected[39m[2m) // indexOf[22m
+Expected substring: [32m"Should have at least 7 characters,[39m
+[32mPasswords do not match"[39m
+Received string:    [31m"Should have at least 7 characters, Passwords do not match"[39m</t>
   </si>
   <si>
     <t>Clark</t>
@@ -180,7 +203,7 @@
     <t>Superman</t>
   </si>
   <si>
-    <t>EMP1001</t>
+    <t>EMP1001333</t>
   </si>
   <si>
     <t>Clark001</t>
@@ -189,6 +212,11 @@
     <t>Disabled</t>
   </si>
   <si>
+    <t xml:space="preserve">[2mexpect([22m[31mreceived[39m[2m).[22mtoContain[2m([22m[32mexpected[39m[2m) // indexOf[22m
+Expected substring: [32m"Successfully Saved"[39m
+Received string:    [31m"Passwords do not match"[39m</t>
+  </si>
+  <si>
     <t>Bruce</t>
   </si>
   <si>
@@ -198,9 +226,6 @@
     <t>Batman</t>
   </si>
   <si>
-    <t>Employee Id Already Exists</t>
-  </si>
-  <si>
     <t>Tony</t>
   </si>
   <si>
@@ -217,27 +242,38 @@
   </si>
   <si>
     <t>Invalid File Type</t>
+  </si>
+  <si>
+    <t>ENOENT: no such file or directory, stat 'C:\Users\manju\Desktop\jspwproject\testdata\test.pdf'</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <color theme="10"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -266,13 +302,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -552,9 +594,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.109375" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -623,467 +665,530 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P11"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" customWidth="1"/>
+    <col min="2" max="3" width="11.88671875" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" customWidth="1"/>
     <col min="7" max="7" width="10.5546875" customWidth="1"/>
     <col min="8" max="8" width="15.33203125" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="40.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" customWidth="1"/>
+    <col min="11" max="11" width="11.88671875" customWidth="1"/>
+    <col min="12" max="12" width="15.88671875" customWidth="1"/>
+    <col min="13" max="13" width="15.6640625" customWidth="1"/>
+    <col min="14" max="14" width="40.109375" customWidth="1"/>
+    <col min="15" max="15" width="50.77734375" customWidth="1"/>
+    <col min="16" max="16" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="J2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="P3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O5" t="s">
+        <v>39</v>
+      </c>
+      <c r="P5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="P6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="P7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="P8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O9" t="s">
+        <v>63</v>
+      </c>
+      <c r="P9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="B10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O10" t="s">
+        <v>37</v>
+      </c>
+      <c r="P10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P1" s="3" t="s">
+      <c r="B11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" s="2" t="s">
+      <c r="K11" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="M11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O11" t="s">
+        <v>73</v>
+      </c>
+      <c r="P11" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K8" s="2">
-        <v>123</v>
-      </c>
-      <c r="L8" s="2">
-        <v>123</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>66</v>
-      </c>
+    </row>
+    <row r="13" ht="14.4" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E13" s="3"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="K7" r:id="rId1"/>
+    <hyperlink ref="L7" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/datasheet.xlsx
+++ b/datasheet.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="69">
   <si>
     <t>Admin</t>
   </si>
@@ -113,26 +113,21 @@
     <t>Successfully Saved</t>
   </si>
   <si>
-    <t xml:space="preserve">[2mexpect([22m[31mreceived[39m[2m).[22mtoContain[2m([22m[32mexpected[39m[2m) // indexOf[22m
-Expected substring: [32m"Successfully Saved"[39m
-Received string:    [31m"something went wrong"[39m</t>
+    <t>SuccessSuccessfully Saved</t>
+  </si>
+  <si>
+    <t>Peter</t>
+  </si>
+  <si>
+    <t>James</t>
+  </si>
+  <si>
+    <t>Parker</t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>Peter</t>
-  </si>
-  <si>
-    <t>James</t>
-  </si>
-  <si>
-    <t>Parker</t>
-  </si>
-  <si>
-    <t>No success toast or validation message found</t>
-  </si>
-  <si>
     <t>Negative</t>
   </si>
   <si>
@@ -148,9 +143,6 @@
     <t>Lee</t>
   </si>
   <si>
-    <t>locator.count: Target page, context or browser has been closed</t>
-  </si>
-  <si>
     <t>Harry</t>
   </si>
   <si>
@@ -184,14 +176,7 @@
     <t>bca</t>
   </si>
   <si>
-    <t xml:space="preserve">Should have at least 7 characters,
-Passwords do not match</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[2mexpect([22m[31mreceived[39m[2m).[22mtoContain[2m([22m[32mexpected[39m[2m) // indexOf[22m
-Expected substring: [32m"Should have at least 7 characters,[39m
-[32mPasswords do not match"[39m
-Received string:    [31m"Should have at least 7 characters, Passwords do not match"[39m</t>
+    <t>Should have at least 7 characters, Passwords do not match</t>
   </si>
   <si>
     <t>Clark</t>
@@ -212,11 +197,6 @@
     <t>Disabled</t>
   </si>
   <si>
-    <t xml:space="preserve">[2mexpect([22m[31mreceived[39m[2m).[22mtoContain[2m([22m[32mexpected[39m[2m) // indexOf[22m
-Expected substring: [32m"Successfully Saved"[39m
-Received string:    [31m"Passwords do not match"[39m</t>
-  </si>
-  <si>
     <t>Bruce</t>
   </si>
   <si>
@@ -238,13 +218,10 @@
     <t>Tony@123</t>
   </si>
   <si>
-    <t>testdata/test.pdf</t>
-  </si>
-  <si>
-    <t>Invalid File Type</t>
-  </si>
-  <si>
-    <t>ENOENT: no such file or directory, stat 'C:\Users\manju\Desktop\jspwproject\testdata\test.pdf'</t>
+    <t>testdata/test1.pdf</t>
+  </si>
+  <si>
+    <t>File type not allowed</t>
   </si>
 </sst>
 </file>
@@ -677,7 +654,7 @@
     <col min="8" max="8" width="15.33203125" customWidth="1"/>
     <col min="9" max="9" width="11.44140625" customWidth="1"/>
     <col min="10" max="10" width="7.88671875" customWidth="1"/>
-    <col min="11" max="11" width="11.88671875" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
     <col min="12" max="12" width="15.88671875" customWidth="1"/>
     <col min="13" max="13" width="15.6640625" customWidth="1"/>
     <col min="14" max="14" width="40.109375" customWidth="1"/>
@@ -780,7 +757,7 @@
         <v>32</v>
       </c>
       <c r="P2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -791,20 +768,20 @@
         <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -817,10 +794,10 @@
         <v>31</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="P3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -828,10 +805,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
@@ -842,7 +819,7 @@
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -852,10 +829,10 @@
         <v>30</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P4" t="s">
         <v>5</v>
@@ -866,10 +843,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>24</v>
@@ -880,7 +857,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -890,10 +867,10 @@
         <v>30</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P5" t="s">
         <v>5</v>
@@ -904,19 +881,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
@@ -941,10 +918,10 @@
         <v>31</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="P6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -952,44 +929,44 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>28</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>30</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P7" t="s">
         <v>5</v>
@@ -1000,47 +977,47 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>28</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>30</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="P8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -1051,33 +1028,35 @@
         <v>22</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="L9" s="3"/>
+      <c r="L9" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="M9" s="3" t="s">
         <v>30</v>
       </c>
@@ -1085,10 +1064,10 @@
         <v>31</v>
       </c>
       <c r="O9" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="P9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -1096,25 +1075,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -1129,10 +1108,10 @@
         <v>31</v>
       </c>
       <c r="O10" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="P10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -1140,26 +1119,26 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>28</v>
@@ -1168,16 +1147,16 @@
         <v>29</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O11" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="P11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" ht="14.4" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
@@ -1187,6 +1166,7 @@
   <hyperlinks>
     <hyperlink ref="K7" r:id="rId1"/>
     <hyperlink ref="L7" r:id="rId2"/>
+    <hyperlink ref="K9" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/datasheet.xlsx
+++ b/datasheet.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="74">
   <si>
     <t>Admin</t>
   </si>
@@ -113,7 +113,12 @@
     <t>Successfully Saved</t>
   </si>
   <si>
-    <t>SuccessSuccessfully Saved</t>
+    <t xml:space="preserve">[2mexpect([22m[31mreceived[39m[2m).[22mtoContain[2m([22m[32mexpected[39m[2m) // indexOf[22m
+Expected substring: [32m"Successfully Saved"[39m
+Received string:    [31m"something went wrong"[39m</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
   <si>
     <t>Peter</t>
@@ -125,7 +130,7 @@
     <t>Parker</t>
   </si>
   <si>
-    <t>No</t>
+    <t>No success toast or validation message found</t>
   </si>
   <si>
     <t>Negative</t>
@@ -143,6 +148,9 @@
     <t>Lee</t>
   </si>
   <si>
+    <t>locator.count: Target page, context or browser has been closed</t>
+  </si>
+  <si>
     <t>Harry</t>
   </si>
   <si>
@@ -176,7 +184,14 @@
     <t>bca</t>
   </si>
   <si>
-    <t>Should have at least 7 characters, Passwords do not match</t>
+    <t xml:space="preserve">Should have at least 7 characters,
+Passwords do not match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[2mexpect([22m[31mreceived[39m[2m).[22mtoContain[2m([22m[32mexpected[39m[2m) // indexOf[22m
+Expected substring: [32m"Should have at least 7 characters,[39m
+[32mPasswords do not match"[39m
+Received string:    [31m"Should have at least 7 characters, Passwords do not match"[39m</t>
   </si>
   <si>
     <t>Clark</t>
@@ -197,6 +212,11 @@
     <t>Disabled</t>
   </si>
   <si>
+    <t xml:space="preserve">[2mexpect([22m[31mreceived[39m[2m).[22mtoContain[2m([22m[32mexpected[39m[2m) // indexOf[22m
+Expected substring: [32m"Successfully Saved"[39m
+Received string:    [31m"Passwords do not match"[39m</t>
+  </si>
+  <si>
     <t>Bruce</t>
   </si>
   <si>
@@ -218,10 +238,13 @@
     <t>Tony@123</t>
   </si>
   <si>
-    <t>testdata/test1.pdf</t>
-  </si>
-  <si>
-    <t>File type not allowed</t>
+    <t>testdata/test.pdf</t>
+  </si>
+  <si>
+    <t>Invalid File Type</t>
+  </si>
+  <si>
+    <t>ENOENT: no such file or directory, stat 'C:\Users\manju\Desktop\jspwproject\testdata\test.pdf'</t>
   </si>
 </sst>
 </file>
@@ -654,7 +677,7 @@
     <col min="8" max="8" width="15.33203125" customWidth="1"/>
     <col min="9" max="9" width="11.44140625" customWidth="1"/>
     <col min="10" max="10" width="7.88671875" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="11" max="11" width="11.88671875" customWidth="1"/>
     <col min="12" max="12" width="15.88671875" customWidth="1"/>
     <col min="13" max="13" width="15.6640625" customWidth="1"/>
     <col min="14" max="14" width="40.109375" customWidth="1"/>
@@ -757,7 +780,7 @@
         <v>32</v>
       </c>
       <c r="P2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -768,20 +791,20 @@
         <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -794,10 +817,10 @@
         <v>31</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="P3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -805,10 +828,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
@@ -819,7 +842,7 @@
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -829,10 +852,10 @@
         <v>30</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P4" t="s">
         <v>5</v>
@@ -843,10 +866,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>24</v>
@@ -857,7 +880,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -867,10 +890,10 @@
         <v>30</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P5" t="s">
         <v>5</v>
@@ -881,19 +904,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
@@ -918,10 +941,10 @@
         <v>31</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="P6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -929,44 +952,44 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>28</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>30</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P7" t="s">
         <v>5</v>
@@ -977,47 +1000,47 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>28</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>30</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="P8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -1028,35 +1051,33 @@
         <v>22</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K9" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="L9" s="3"/>
       <c r="M9" s="3" t="s">
         <v>30</v>
       </c>
@@ -1064,10 +1085,10 @@
         <v>31</v>
       </c>
       <c r="O9" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="P9" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -1075,25 +1096,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="H10" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -1108,10 +1129,10 @@
         <v>31</v>
       </c>
       <c r="O10" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="P10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -1119,26 +1140,26 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>28</v>
@@ -1147,16 +1168,16 @@
         <v>29</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O11" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="P11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" ht="14.4" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
@@ -1166,7 +1187,6 @@
   <hyperlinks>
     <hyperlink ref="K7" r:id="rId1"/>
     <hyperlink ref="L7" r:id="rId2"/>
-    <hyperlink ref="K9" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/datasheet.xlsx
+++ b/datasheet.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="69">
   <si>
     <t>Admin</t>
   </si>
@@ -113,26 +113,21 @@
     <t>Successfully Saved</t>
   </si>
   <si>
-    <t xml:space="preserve">[2mexpect([22m[31mreceived[39m[2m).[22mtoContain[2m([22m[32mexpected[39m[2m) // indexOf[22m
-Expected substring: [32m"Successfully Saved"[39m
-Received string:    [31m"something went wrong"[39m</t>
+    <t>SuccessSuccessfully Saved</t>
+  </si>
+  <si>
+    <t>Peter</t>
+  </si>
+  <si>
+    <t>James</t>
+  </si>
+  <si>
+    <t>Parker</t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>Peter</t>
-  </si>
-  <si>
-    <t>James</t>
-  </si>
-  <si>
-    <t>Parker</t>
-  </si>
-  <si>
-    <t>No success toast or validation message found</t>
-  </si>
-  <si>
     <t>Negative</t>
   </si>
   <si>
@@ -148,9 +143,6 @@
     <t>Lee</t>
   </si>
   <si>
-    <t>locator.count: Target page, context or browser has been closed</t>
-  </si>
-  <si>
     <t>Harry</t>
   </si>
   <si>
@@ -184,14 +176,7 @@
     <t>bca</t>
   </si>
   <si>
-    <t xml:space="preserve">Should have at least 7 characters,
-Passwords do not match</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[2mexpect([22m[31mreceived[39m[2m).[22mtoContain[2m([22m[32mexpected[39m[2m) // indexOf[22m
-Expected substring: [32m"Should have at least 7 characters,[39m
-[32mPasswords do not match"[39m
-Received string:    [31m"Should have at least 7 characters, Passwords do not match"[39m</t>
+    <t>Should have at least 7 characters,Passwords do not match</t>
   </si>
   <si>
     <t>Clark</t>
@@ -212,11 +197,6 @@
     <t>Disabled</t>
   </si>
   <si>
-    <t xml:space="preserve">[2mexpect([22m[31mreceived[39m[2m).[22mtoContain[2m([22m[32mexpected[39m[2m) // indexOf[22m
-Expected substring: [32m"Successfully Saved"[39m
-Received string:    [31m"Passwords do not match"[39m</t>
-  </si>
-  <si>
     <t>Bruce</t>
   </si>
   <si>
@@ -238,13 +218,10 @@
     <t>Tony@123</t>
   </si>
   <si>
-    <t>testdata/test.pdf</t>
-  </si>
-  <si>
-    <t>Invalid File Type</t>
-  </si>
-  <si>
-    <t>ENOENT: no such file or directory, stat 'C:\Users\manju\Desktop\jspwproject\testdata\test.pdf'</t>
+    <t>testdata/test1.pdf</t>
+  </si>
+  <si>
+    <t>File type not allowed</t>
   </si>
 </sst>
 </file>
@@ -780,7 +757,7 @@
         <v>32</v>
       </c>
       <c r="P2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -791,20 +768,20 @@
         <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -817,10 +794,10 @@
         <v>31</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="P3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -828,10 +805,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
@@ -842,7 +819,7 @@
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -852,10 +829,10 @@
         <v>30</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P4" t="s">
         <v>5</v>
@@ -866,10 +843,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>24</v>
@@ -880,7 +857,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -890,10 +867,10 @@
         <v>30</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P5" t="s">
         <v>5</v>
@@ -904,19 +881,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
@@ -941,10 +918,10 @@
         <v>31</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="P6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -952,44 +929,44 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>28</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>30</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P7" t="s">
         <v>5</v>
@@ -1000,47 +977,47 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>28</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>30</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="P8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -1051,33 +1028,35 @@
         <v>22</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="L9" s="3"/>
+      <c r="L9" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="M9" s="3" t="s">
         <v>30</v>
       </c>
@@ -1085,10 +1064,10 @@
         <v>31</v>
       </c>
       <c r="O9" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="P9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -1096,25 +1075,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -1129,10 +1108,10 @@
         <v>31</v>
       </c>
       <c r="O10" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="P10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -1140,26 +1119,26 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>28</v>
@@ -1168,16 +1147,16 @@
         <v>29</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O11" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="P11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" ht="14.4" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">

--- a/datasheet.xlsx
+++ b/datasheet.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30253CE5-70A1-4F67-9174-FB9CA5D3B923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="login" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="userCreation" state="visible" r:id="rId5"/>
+    <sheet name="login" sheetId="1" r:id="rId1"/>
+    <sheet name="userCreation" sheetId="2" r:id="rId2"/>
+    <sheet name="AdminUserManagementUser" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="115">
   <si>
     <t>Admin</t>
   </si>
@@ -222,35 +224,205 @@
   </si>
   <si>
     <t>File type not allowed</t>
+  </si>
+  <si>
+    <t>TestAction</t>
+  </si>
+  <si>
+    <t>UserRole</t>
+  </si>
+  <si>
+    <t>EmployeeName</t>
+  </si>
+  <si>
+    <t>UserStatus</t>
+  </si>
+  <si>
+    <t>SearchUser</t>
+  </si>
+  <si>
+    <t>James Tester Bach</t>
+  </si>
+  <si>
+    <t>cac5265454sc</t>
+  </si>
+  <si>
+    <t>Exception Occurred: [2mexpect([22m[31mreceived[39m[2m).[22mtoContain[2m([22m[32mexpected[39m[2m) // indexOf[22m
+Expected substring: [32m"username not found in table"[39m
+Received string:    [31m"employee does not exist"[39m</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>SearchUserByRole</t>
+  </si>
+  <si>
+    <t>ESS</t>
+  </si>
+  <si>
+    <t>employee does not exist</t>
+  </si>
+  <si>
+    <t>Exception Occurred: [2mexpect([22m[31mreceived[39m[2m).[22mtoContain[2m([22m[32mexpected[39m[2m) // indexOf[22m
+Expected substring: [32m"employee does not exist"[39m
+Received string:    [31m"username not found in table"[39m</t>
+  </si>
+  <si>
+    <t>AddUserDynamic</t>
+  </si>
+  <si>
+    <t>John Larsen</t>
+  </si>
+  <si>
+    <t>AUTO_GENERATE</t>
+  </si>
+  <si>
+    <t>Admin@123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exception Occurred: locator.fill: Test timeout of 120000ms exceeded.
+Call log:
+[2m  - waiting for getByRole('textbox', { name: 'Password', exact: true })[22m
+</t>
+  </si>
+  <si>
+    <t>ResetFilter</t>
+  </si>
+  <si>
+    <t>All fields reset successfully</t>
+  </si>
+  <si>
+    <t>CancelAddUser</t>
+  </si>
+  <si>
+    <t>TempUser01</t>
+  </si>
+  <si>
+    <t>Navigated back successfully</t>
+  </si>
+  <si>
+    <t>NavigateBackToUserList</t>
+  </si>
+  <si>
+    <t>User list page displayed successfully</t>
+  </si>
+  <si>
+    <t>AddDuplicateUser</t>
+  </si>
+  <si>
+    <t>Save failed</t>
+  </si>
+  <si>
+    <t>InvalidEmployee</t>
+  </si>
+  <si>
+    <t>Invalid Employee</t>
+  </si>
+  <si>
+    <t>User999</t>
+  </si>
+  <si>
+    <t>RequiredUsername</t>
+  </si>
+  <si>
+    <t>PasswordMismatch</t>
+  </si>
+  <si>
+    <t>User123</t>
+  </si>
+  <si>
+    <t>Admin123</t>
+  </si>
+  <si>
+    <t>John Doe</t>
+  </si>
+  <si>
+    <t>User111</t>
+  </si>
+  <si>
+    <t>User Role Required</t>
+  </si>
+  <si>
+    <t>Bruce Wayne</t>
+  </si>
+  <si>
+    <t>Batman001</t>
+  </si>
+  <si>
+    <t>Wayne@123</t>
+  </si>
+  <si>
+    <t>Tony Stark</t>
+  </si>
+  <si>
+    <t>Ironman01</t>
+  </si>
+  <si>
+    <t>Stark@123</t>
+  </si>
+  <si>
+    <t>Peter Parker</t>
+  </si>
+  <si>
+    <t>Peter123</t>
+  </si>
+  <si>
+    <t>Already Exists</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFCD3131"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -267,7 +439,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -275,11 +447,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -292,6 +479,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -571,9 +775,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.109375" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -642,9 +846,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="11.88671875" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
@@ -712,7 +916,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -760,7 +964,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -800,7 +1004,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -838,7 +1042,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -876,7 +1080,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -924,7 +1128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -972,7 +1176,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1020,7 +1224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -1070,7 +1274,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -1114,7 +1318,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -1159,15 +1363,571 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" ht="14.4" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E13" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K7" r:id="rId1"/>
-    <hyperlink ref="L7" r:id="rId2"/>
+    <hyperlink ref="K7" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="L7" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="13.77734375" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" customWidth="1"/>
+    <col min="8" max="8" width="8.5546875" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" customWidth="1"/>
+    <col min="11" max="12" width="21.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" s="1" customFormat="1" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="L5" s="10"/>
+      <c r="M5" s="3"/>
+    </row>
+    <row r="6" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="L6" s="10"/>
+      <c r="M6" s="3"/>
+    </row>
+    <row r="7" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="L7" s="10"/>
+      <c r="M7" s="3"/>
+    </row>
+    <row r="8" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="L8" s="10"/>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="L9" s="10"/>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
+        <v>9</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="L10" s="10"/>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="L11" s="10"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="9">
+        <v>11</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K12" s="9"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="9">
+        <v>12</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="9"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9">
+        <v>13</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="9"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9">
+        <v>14</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="K15" s="9"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="9"/>
+    </row>
+    <row r="17" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/datasheet.xlsx
+++ b/datasheet.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30253CE5-70A1-4F67-9174-FB9CA5D3B923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="login" sheetId="1" r:id="rId1"/>
-    <sheet name="userCreation" sheetId="2" r:id="rId2"/>
-    <sheet name="AdminUserManagementUser" sheetId="3" r:id="rId3"/>
+    <sheet sheetId="1" name="login" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="userCreation" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="AdminUserManagementUser" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="116">
   <si>
     <t>Admin</t>
   </si>
@@ -238,7 +237,7 @@
     <t>UserStatus</t>
   </si>
   <si>
-    <t>SearchUser</t>
+    <t>SearchUserByAll</t>
   </si>
   <si>
     <t>James Tester Bach</t>
@@ -247,12 +246,13 @@
     <t>cac5265454sc</t>
   </si>
   <si>
-    <t>Exception Occurred: [2mexpect([22m[31mreceived[39m[2m).[22mtoContain[2m([22m[32mexpected[39m[2m) // indexOf[22m
-Expected substring: [32m"username not found in table"[39m
-Received string:    [31m"employee does not exist"[39m</t>
-  </si>
-  <si>
-    <t>Fail</t>
+    <t>no records found</t>
+  </si>
+  <si>
+    <t>No Records Found</t>
+  </si>
+  <si>
+    <t>Pass</t>
   </si>
   <si>
     <t>SearchUserByRole</t>
@@ -261,12 +261,7 @@
     <t>ESS</t>
   </si>
   <si>
-    <t>employee does not exist</t>
-  </si>
-  <si>
-    <t>Exception Occurred: [2mexpect([22m[31mreceived[39m[2m).[22mtoContain[2m([22m[32mexpected[39m[2m) // indexOf[22m
-Expected substring: [32m"employee does not exist"[39m
-Received string:    [31m"username not found in table"[39m</t>
+    <t>Records Found</t>
   </si>
   <si>
     <t>AddUserDynamic</t>
@@ -287,6 +282,9 @@
 </t>
   </si>
   <si>
+    <t>Fail</t>
+  </si>
+  <si>
     <t>ResetFilter</t>
   </si>
   <si>
@@ -374,55 +372,51 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FF1F1F1F"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color rgb="FF1F1F1F"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <b/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFCD3131"/>
-      <name val="Courier New"/>
-      <family val="3"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -466,7 +460,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -491,11 +485,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -775,9 +768,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.109375" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -846,9 +839,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="2" max="3" width="11.88671875" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
@@ -916,7 +909,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -964,7 +957,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1004,7 +997,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1042,7 +1035,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1080,7 +1073,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1128,7 +1121,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1176,7 +1169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1224,7 +1217,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -1274,7 +1267,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -1318,7 +1311,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -1363,23 +1356,23 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="14.4" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E13" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K7" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="L7" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="K7" r:id="rId1"/>
+    <hyperlink ref="L7" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="13.77734375" customWidth="1"/>
     <col min="5" max="5" width="8.5546875" customWidth="1"/>
@@ -1388,10 +1381,11 @@
     <col min="8" max="8" width="8.5546875" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" customWidth="1"/>
     <col min="10" max="10" width="11.5546875" customWidth="1"/>
-    <col min="11" max="12" width="21.6640625" customWidth="1"/>
+    <col min="11" max="11" width="21.6640625" customWidth="1"/>
+    <col min="12" max="12" width="32.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" ht="28.8" customHeight="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>9</v>
       </c>
@@ -1432,7 +1426,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -1459,17 +1453,17 @@
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
-      <c r="K2" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="L2" s="10" t="s">
+      <c r="K2" s="10" t="s">
         <v>76</v>
       </c>
+      <c r="L2" s="11" t="s">
+        <v>77</v>
+      </c>
       <c r="M2" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -1480,10 +1474,10 @@
         <v>23</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
@@ -1492,17 +1486,17 @@
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
-      <c r="K3" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="L3" s="10" t="s">
+      <c r="K3" s="10" t="s">
         <v>81</v>
       </c>
+      <c r="L3" s="11" t="s">
+        <v>81</v>
+      </c>
       <c r="M3" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -1510,7 +1504,7 @@
         <v>22</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>82</v>
@@ -1536,14 +1530,14 @@
       <c r="K4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="11" t="s">
         <v>86</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -1554,7 +1548,7 @@
         <v>36</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="9" t="s">
@@ -1569,12 +1563,12 @@
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="L5" s="10"/>
+        <v>89</v>
+      </c>
+      <c r="L5" s="11"/>
       <c r="M5" s="3"/>
     </row>
-    <row r="6" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -1585,7 +1579,7 @@
         <v>36</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>0</v>
@@ -1594,7 +1588,7 @@
         <v>83</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>28</v>
@@ -1606,12 +1600,12 @@
         <v>85</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="L6" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="L6" s="11"/>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -1622,7 +1616,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -1631,12 +1625,12 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="L7" s="10"/>
+        <v>94</v>
+      </c>
+      <c r="L7" s="11"/>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="43.2" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -1647,7 +1641,7 @@
         <v>36</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>0</v>
@@ -1668,12 +1662,12 @@
         <v>85</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="L8" s="10"/>
+        <v>96</v>
+      </c>
+      <c r="L8" s="11"/>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="72" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -1684,16 +1678,16 @@
         <v>36</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>28</v>
@@ -1705,12 +1699,12 @@
         <v>85</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="L9" s="10"/>
+        <v>98</v>
+      </c>
+      <c r="L9" s="11"/>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="43.2" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>9</v>
       </c>
@@ -1721,7 +1715,7 @@
         <v>36</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>0</v>
@@ -1740,12 +1734,12 @@
         <v>85</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="L10" s="10"/>
+        <v>96</v>
+      </c>
+      <c r="L10" s="11"/>
       <c r="M10" s="3"/>
     </row>
-    <row r="11" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="43.2" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>10</v>
       </c>
@@ -1756,16 +1750,16 @@
         <v>36</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>83</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>28</v>
@@ -1774,15 +1768,15 @@
         <v>85</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="L11" s="10"/>
+        <v>96</v>
+      </c>
+      <c r="L11" s="11"/>
       <c r="M11" s="3"/>
     </row>
-    <row r="12" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>11</v>
       </c>
@@ -1794,10 +1788,10 @@
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>28</v>
@@ -1809,13 +1803,13 @@
         <v>85</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K12" s="9"/>
-      <c r="L12" s="10"/>
+      <c r="L12" s="11"/>
       <c r="M12" s="3"/>
     </row>
-    <row r="13" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>12</v>
       </c>
@@ -1826,31 +1820,31 @@
         <v>36</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>59</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>31</v>
       </c>
       <c r="K13" s="9"/>
-      <c r="L13" s="10"/>
+      <c r="L13" s="11"/>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>13</v>
       </c>
@@ -1864,28 +1858,28 @@
         <v>0</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>31</v>
       </c>
       <c r="K14" s="9"/>
-      <c r="L14" s="10"/>
+      <c r="L14" s="11"/>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>14</v>
       </c>
@@ -1896,13 +1890,13 @@
         <v>36</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>28</v>
@@ -1914,20 +1908,20 @@
         <v>85</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K15" s="9"/>
-      <c r="L15" s="10"/>
+      <c r="L15" s="11"/>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" ht="14.4" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C16" s="9"/>
     </row>
-    <row r="17" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" ht="14.4" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C17" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/datasheet.xlsx
+++ b/datasheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="118">
   <si>
     <t>Admin</t>
   </si>
@@ -237,6 +237,9 @@
     <t>UserStatus</t>
   </si>
   <si>
+    <t>NO</t>
+  </si>
+  <si>
     <t>SearchUserByAll</t>
   </si>
   <si>
@@ -267,25 +270,27 @@
     <t>AddUserDynamic</t>
   </si>
   <si>
+    <t>Ikshvaku</t>
+  </si>
+  <si>
+    <t>IkshvakuRamaNarayan</t>
+  </si>
+  <si>
+    <t>Admin@123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exception Occurred: [2mexpect([22m[31mreceived[39m[2m).[22mtoContain[2m([22m[32mexpected[39m[2m) // indexOf[22m
+Expected substring: [32m"successfully saved"[39m
+Received string:    [31m"save failed"[39m</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>ResetFilter</t>
+  </si>
+  <si>
     <t>John Larsen</t>
-  </si>
-  <si>
-    <t>AUTO_GENERATE</t>
-  </si>
-  <si>
-    <t>Admin@123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exception Occurred: locator.fill: Test timeout of 120000ms exceeded.
-Call log:
-[2m  - waiting for getByRole('textbox', { name: 'Password', exact: true })[22m
-</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>ResetFilter</t>
   </si>
   <si>
     <t>All fields reset successfully</t>
@@ -1377,7 +1382,7 @@
     <col min="4" max="4" width="13.77734375" customWidth="1"/>
     <col min="5" max="5" width="8.5546875" customWidth="1"/>
     <col min="6" max="6" width="15.6640625" customWidth="1"/>
-    <col min="7" max="7" width="11.77734375" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" customWidth="1"/>
     <col min="8" max="8" width="8.5546875" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" customWidth="1"/>
     <col min="10" max="10" width="11.5546875" customWidth="1"/>
@@ -1434,19 +1439,19 @@
         <v>22</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>28</v>
@@ -1454,13 +1459,13 @@
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
       <c r="K2" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1471,13 +1476,13 @@
         <v>22</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
@@ -1487,13 +1492,13 @@
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
       <c r="K3" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1504,37 +1509,37 @@
         <v>22</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>31</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1548,11 +1553,11 @@
         <v>36</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="9" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>0</v>
@@ -1563,7 +1568,7 @@
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L5" s="11"/>
       <c r="M5" s="3"/>
@@ -1579,28 +1584,28 @@
         <v>36</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L6" s="11"/>
       <c r="M6" s="3"/>
@@ -1616,7 +1621,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -1625,7 +1630,7 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L7" s="11"/>
       <c r="M7" s="3"/>
@@ -1641,13 +1646,13 @@
         <v>36</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>0</v>
@@ -1656,13 +1661,13 @@
         <v>28</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L8" s="11"/>
       <c r="M8" s="3"/>
@@ -1678,28 +1683,28 @@
         <v>36</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L9" s="11"/>
       <c r="M9" s="3"/>
@@ -1715,26 +1720,26 @@
         <v>36</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G10" s="9"/>
       <c r="H10" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L10" s="11"/>
       <c r="M10" s="3"/>
@@ -1750,28 +1755,28 @@
         <v>36</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L11" s="11"/>
       <c r="M11" s="3"/>
@@ -1788,22 +1793,22 @@
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="11"/>
@@ -1820,22 +1825,22 @@
         <v>36</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>59</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>31</v>
@@ -1858,19 +1863,19 @@
         <v>0</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>31</v>
@@ -1890,25 +1895,25 @@
         <v>36</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="11"/>

--- a/datasheet.xlsx
+++ b/datasheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="117">
   <si>
     <t>Admin</t>
   </si>
@@ -235,9 +235,6 @@
   </si>
   <si>
     <t>UserStatus</t>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
   <si>
     <t>SearchUserByAll</t>
@@ -465,7 +462,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -488,6 +485,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1387,7 +1387,7 @@
     <col min="9" max="9" width="8.6640625" customWidth="1"/>
     <col min="10" max="10" width="11.5546875" customWidth="1"/>
     <col min="11" max="11" width="21.6640625" customWidth="1"/>
-    <col min="12" max="12" width="32.88671875" customWidth="1"/>
+    <col min="12" max="12" width="32.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.8" customHeight="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1438,34 +1438,34 @@
       <c r="B2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>73</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>74</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F2" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>75</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>76</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="L2" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="M2" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="3" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1475,14 +1475,14 @@
       <c r="B3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>73</v>
+      <c r="C3" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="D3" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>80</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>81</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
@@ -1491,14 +1491,14 @@
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
-      <c r="K3" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>82</v>
+      <c r="K3" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>81</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1509,37 +1509,37 @@
         <v>22</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="F4" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="5" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1549,15 +1549,17 @@
       <c r="B5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>36</v>
+      <c r="C5" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>0</v>
@@ -1565,13 +1567,21 @@
       <c r="H5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
+      <c r="I5" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>85</v>
+      </c>
       <c r="K5" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="L5" s="11"/>
-      <c r="M5" s="3"/>
+        <v>90</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="6" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
@@ -1584,30 +1594,30 @@
         <v>36</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="L6" s="11"/>
+        <v>93</v>
+      </c>
+      <c r="L6" s="12"/>
       <c r="M6" s="3"/>
     </row>
     <row r="7" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1621,7 +1631,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -1630,9 +1640,9 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L7" s="11"/>
+        <v>95</v>
+      </c>
+      <c r="L7" s="12"/>
       <c r="M7" s="3"/>
     </row>
     <row r="8" ht="43.2" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1646,13 +1656,13 @@
         <v>36</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>0</v>
@@ -1661,15 +1671,15 @@
         <v>28</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L8" s="11"/>
+        <v>97</v>
+      </c>
+      <c r="L8" s="12"/>
       <c r="M8" s="3"/>
     </row>
     <row r="9" ht="72" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1683,30 +1693,30 @@
         <v>36</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F9" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>100</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>101</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="L9" s="11"/>
+        <v>99</v>
+      </c>
+      <c r="L9" s="12"/>
       <c r="M9" s="3"/>
     </row>
     <row r="10" ht="43.2" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1720,28 +1730,28 @@
         <v>36</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G10" s="9"/>
       <c r="H10" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L10" s="11"/>
+        <v>97</v>
+      </c>
+      <c r="L10" s="12"/>
       <c r="M10" s="3"/>
     </row>
     <row r="11" ht="43.2" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1755,30 +1765,30 @@
         <v>36</v>
       </c>
       <c r="D11" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="G11" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>104</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="L11" s="11"/>
+        <v>97</v>
+      </c>
+      <c r="L11" s="12"/>
       <c r="M11" s="3"/>
     </row>
     <row r="12" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1793,25 +1803,25 @@
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>106</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>107</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K12" s="9"/>
-      <c r="L12" s="11"/>
+      <c r="L12" s="12"/>
       <c r="M12" s="3"/>
     </row>
     <row r="13" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1825,28 +1835,28 @@
         <v>36</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E13" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>109</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>110</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>59</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>31</v>
       </c>
       <c r="K13" s="9"/>
-      <c r="L13" s="11"/>
+      <c r="L13" s="12"/>
       <c r="M13" s="3"/>
     </row>
     <row r="14" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1863,25 +1873,25 @@
         <v>0</v>
       </c>
       <c r="E14" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>112</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>113</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>31</v>
       </c>
       <c r="K14" s="9"/>
-      <c r="L14" s="11"/>
+      <c r="L14" s="12"/>
       <c r="M14" s="3"/>
     </row>
     <row r="15" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1895,28 +1905,28 @@
         <v>36</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E15" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F15" s="9" t="s">
         <v>115</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>116</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K15" s="9"/>
-      <c r="L15" s="11"/>
+      <c r="L15" s="12"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" ht="14.4" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">

--- a/datasheet.xlsx
+++ b/datasheet.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A50611C9-979A-48C9-9E38-9728C859D38C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="login" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="userCreation" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="AdminUserManagementUser" state="visible" r:id="rId6"/>
+    <sheet name="login" sheetId="1" r:id="rId1"/>
+    <sheet name="userCreation" sheetId="2" r:id="rId2"/>
+    <sheet name="AdminUserManagementUser" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="116">
   <si>
     <t>Admin</t>
   </si>
@@ -274,11 +275,6 @@
   </si>
   <si>
     <t>Admin@123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exception Occurred: [2mexpect([22m[31mreceived[39m[2m).[22mtoContain[2m([22m[32mexpected[39m[2m) // indexOf[22m
-Expected substring: [32m"successfully saved"[39m
-Received string:    [31m"save failed"[39m</t>
   </si>
   <si>
     <t>Fail</t>
@@ -374,51 +370,51 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -773,9 +769,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.109375" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -844,9 +840,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="11.88671875" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
@@ -914,7 +910,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -962,7 +958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1002,7 +998,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1040,7 +1036,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1078,7 +1074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1126,7 +1122,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1174,7 +1170,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1222,7 +1218,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -1272,7 +1268,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -1316,7 +1312,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -1361,23 +1357,23 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" ht="14.4" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E13" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K7" r:id="rId1"/>
-    <hyperlink ref="L7" r:id="rId2"/>
+    <hyperlink ref="K7" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="L7" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="13.77734375" customWidth="1"/>
     <col min="5" max="5" width="8.5546875" customWidth="1"/>
@@ -1390,7 +1386,7 @@
     <col min="12" max="12" width="32.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" customHeight="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="1" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>9</v>
       </c>
@@ -1431,7 +1427,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -1468,7 +1464,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -1501,7 +1497,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -1535,14 +1531,12 @@
       <c r="K4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="L4" s="12"/>
+      <c r="M4" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="M4" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -1553,13 +1547,13 @@
         <v>23</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>0</v>
@@ -1574,16 +1568,16 @@
         <v>85</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="6" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -1594,16 +1588,16 @@
         <v>36</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>28</v>
@@ -1615,12 +1609,12 @@
         <v>85</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -1631,7 +1625,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -1640,12 +1634,12 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L7" s="12"/>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" ht="43.2" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -1656,13 +1650,13 @@
         <v>36</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>0</v>
@@ -1677,12 +1671,12 @@
         <v>85</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L8" s="12"/>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" ht="72" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -1693,16 +1687,16 @@
         <v>36</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F9" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>28</v>
@@ -1714,12 +1708,12 @@
         <v>85</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L9" s="12"/>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" ht="43.2" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>9</v>
       </c>
@@ -1730,13 +1724,13 @@
         <v>36</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G10" s="9"/>
       <c r="H10" s="9" t="s">
@@ -1749,12 +1743,12 @@
         <v>85</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L10" s="12"/>
       <c r="M10" s="3"/>
     </row>
-    <row r="11" ht="43.2" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>10</v>
       </c>
@@ -1765,16 +1759,16 @@
         <v>36</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>28</v>
@@ -1783,15 +1777,15 @@
         <v>85</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L11" s="12"/>
       <c r="M11" s="3"/>
     </row>
-    <row r="12" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>11</v>
       </c>
@@ -1803,10 +1797,10 @@
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>28</v>
@@ -1818,13 +1812,13 @@
         <v>85</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="12"/>
       <c r="M12" s="3"/>
     </row>
-    <row r="13" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>12</v>
       </c>
@@ -1838,19 +1832,19 @@
         <v>80</v>
       </c>
       <c r="E13" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>108</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>109</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>59</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>31</v>
@@ -1859,7 +1853,7 @@
       <c r="L13" s="12"/>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>13</v>
       </c>
@@ -1873,19 +1867,19 @@
         <v>0</v>
       </c>
       <c r="E14" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>111</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>112</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>31</v>
@@ -1894,7 +1888,7 @@
       <c r="L14" s="12"/>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>14</v>
       </c>
@@ -1908,10 +1902,10 @@
         <v>80</v>
       </c>
       <c r="E15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F15" s="9" t="s">
         <v>114</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>115</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>28</v>
@@ -1923,20 +1917,20 @@
         <v>85</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="12"/>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" ht="14.4" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="9"/>
     </row>
-    <row r="17" ht="14.4" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/datasheet.xlsx
+++ b/datasheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A50611C9-979A-48C9-9E38-9728C859D38C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C5DFD7-0F5E-4B26-8D20-06452AF19061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="113">
   <si>
     <t>Admin</t>
   </si>
@@ -250,12 +250,6 @@
     <t>no records found</t>
   </si>
   <si>
-    <t>No Records Found</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
-  <si>
     <t>SearchUserByRole</t>
   </si>
   <si>
@@ -275,9 +269,6 @@
   </si>
   <si>
     <t>Admin@123</t>
-  </si>
-  <si>
-    <t>Fail</t>
   </si>
   <si>
     <t>ResetFilter</t>
@@ -1427,7 +1418,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -1457,14 +1448,10 @@
       <c r="K2" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="L2" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L2" s="12"/>
+      <c r="M2" s="3"/>
+    </row>
+    <row r="3" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -1475,10 +1462,10 @@
         <v>23</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
@@ -1488,14 +1475,10 @@
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
       <c r="K3" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="L3" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>78</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="L3" s="12"/>
+      <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
@@ -1508,33 +1491,31 @@
         <v>36</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" s="9" t="s">
         <v>82</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>84</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>31</v>
       </c>
       <c r="L4" s="12"/>
-      <c r="M4" s="3" t="s">
-        <v>86</v>
-      </c>
+      <c r="M4" s="3"/>
     </row>
     <row r="5" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
@@ -1547,13 +1528,13 @@
         <v>23</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>0</v>
@@ -1562,20 +1543,16 @@
         <v>28</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>78</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="L5" s="12"/>
+      <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
@@ -1588,28 +1565,28 @@
         <v>36</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F6" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>88</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>91</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="3"/>
@@ -1625,7 +1602,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -1634,7 +1611,7 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L7" s="12"/>
       <c r="M7" s="3"/>
@@ -1650,13 +1627,13 @@
         <v>36</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>0</v>
@@ -1665,13 +1642,13 @@
         <v>28</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L8" s="12"/>
       <c r="M8" s="3"/>
@@ -1687,28 +1664,28 @@
         <v>36</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L9" s="12"/>
       <c r="M9" s="3"/>
@@ -1724,26 +1701,26 @@
         <v>36</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G10" s="9"/>
       <c r="H10" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L10" s="12"/>
       <c r="M10" s="3"/>
@@ -1759,28 +1736,28 @@
         <v>36</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L11" s="12"/>
       <c r="M11" s="3"/>
@@ -1797,22 +1774,22 @@
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="12"/>
@@ -1829,22 +1806,22 @@
         <v>36</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>59</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>31</v>
@@ -1867,19 +1844,19 @@
         <v>0</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>31</v>
@@ -1899,25 +1876,25 @@
         <v>36</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="12"/>

--- a/datasheet.xlsx
+++ b/datasheet.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C5DFD7-0F5E-4B26-8D20-06452AF19061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="login" sheetId="1" r:id="rId1"/>
-    <sheet name="userCreation" sheetId="2" r:id="rId2"/>
-    <sheet name="AdminUserManagementUser" sheetId="3" r:id="rId3"/>
+    <sheet sheetId="1" name="login" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="userCreation" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="AdminUserManagementUser" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="115">
   <si>
     <t>Admin</t>
   </si>
@@ -248,6 +247,12 @@
   </si>
   <si>
     <t>no records found</t>
+  </si>
+  <si>
+    <t>No Records Found</t>
+  </si>
+  <si>
+    <t>Pass</t>
   </si>
   <si>
     <t>SearchUserByRole</t>
@@ -361,51 +366,51 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FF1F1F1F"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color rgb="FF1F1F1F"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -760,9 +765,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.109375" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -831,9 +836,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="2" max="3" width="11.88671875" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
@@ -901,7 +906,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -949,7 +954,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -989,7 +994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1027,7 +1032,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1065,7 +1070,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1113,7 +1118,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1161,7 +1166,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1209,7 +1214,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -1259,7 +1264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -1303,7 +1308,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -1348,23 +1353,23 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="14.4" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E13" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K7" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="L7" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="K7" r:id="rId1"/>
+    <hyperlink ref="L7" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="13.77734375" customWidth="1"/>
     <col min="5" max="5" width="8.5546875" customWidth="1"/>
@@ -1377,7 +1382,7 @@
     <col min="12" max="12" width="32.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28.8" customHeight="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>9</v>
       </c>
@@ -1418,7 +1423,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -1448,10 +1453,14 @@
       <c r="K2" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="L2" s="12"/>
-      <c r="M2" s="3"/>
-    </row>
-    <row r="3" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L2" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -1462,10 +1471,10 @@
         <v>23</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
@@ -1475,12 +1484,16 @@
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
       <c r="K3" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="L3" s="12"/>
-      <c r="M3" s="3"/>
-    </row>
-    <row r="4" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -1491,25 +1504,25 @@
         <v>36</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="F4" s="9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>31</v>
@@ -1517,7 +1530,7 @@
       <c r="L4" s="12"/>
       <c r="M4" s="3"/>
     </row>
-    <row r="5" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -1528,13 +1541,13 @@
         <v>23</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>0</v>
@@ -1543,55 +1556,63 @@
         <v>28</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="L5" s="12"/>
-      <c r="M5" s="3"/>
-    </row>
-    <row r="6" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>36</v>
+      <c r="C6" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="L6" s="12"/>
-      <c r="M6" s="3"/>
-    </row>
-    <row r="7" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -1599,10 +1620,10 @@
         <v>22</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -1611,12 +1632,16 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="L7" s="12"/>
-      <c r="M7" s="3"/>
-    </row>
-    <row r="8" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" ht="43.2" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -1624,36 +1649,40 @@
         <v>37</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="L8" s="12"/>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" ht="72" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -1664,33 +1693,33 @@
         <v>36</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L9" s="12"/>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="43.2" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>9</v>
       </c>
@@ -1701,31 +1730,31 @@
         <v>36</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>0</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G10" s="9"/>
       <c r="H10" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L10" s="12"/>
       <c r="M10" s="3"/>
     </row>
-    <row r="11" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="43.2" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>10</v>
       </c>
@@ -1736,33 +1765,33 @@
         <v>36</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L11" s="12"/>
       <c r="M11" s="3"/>
     </row>
-    <row r="12" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>11</v>
       </c>
@@ -1774,28 +1803,28 @@
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="12"/>
       <c r="M12" s="3"/>
     </row>
-    <row r="13" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>12</v>
       </c>
@@ -1806,22 +1835,22 @@
         <v>36</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>59</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>31</v>
@@ -1830,7 +1859,7 @@
       <c r="L13" s="12"/>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>13</v>
       </c>
@@ -1844,19 +1873,19 @@
         <v>0</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>31</v>
@@ -1865,7 +1894,7 @@
       <c r="L14" s="12"/>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>14</v>
       </c>
@@ -1876,38 +1905,38 @@
         <v>36</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="12"/>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" ht="14.4" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C16" s="9"/>
     </row>
-    <row r="17" spans="3:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" ht="14.4" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C17" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/datasheet.xlsx
+++ b/datasheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="104">
   <si>
     <t>Admin</t>
   </si>
@@ -315,6 +315,9 @@
     <t>User999</t>
   </si>
   <si>
+    <t>Invalid</t>
+  </si>
+  <si>
     <t>RequiredUsername</t>
   </si>
   <si>
@@ -325,42 +328,6 @@
   </si>
   <si>
     <t>Admin123</t>
-  </si>
-  <si>
-    <t>John Doe</t>
-  </si>
-  <si>
-    <t>User111</t>
-  </si>
-  <si>
-    <t>User Role Required</t>
-  </si>
-  <si>
-    <t>Bruce Wayne</t>
-  </si>
-  <si>
-    <t>Batman001</t>
-  </si>
-  <si>
-    <t>Wayne@123</t>
-  </si>
-  <si>
-    <t>Tony Stark</t>
-  </si>
-  <si>
-    <t>Ironman01</t>
-  </si>
-  <si>
-    <t>Stark@123</t>
-  </si>
-  <si>
-    <t>Peter Parker</t>
-  </si>
-  <si>
-    <t>Peter123</t>
-  </si>
-  <si>
-    <t>Already Exists</t>
   </si>
 </sst>
 </file>
@@ -1368,7 +1335,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="13.77734375" customWidth="1"/>
@@ -1500,7 +1467,7 @@
       <c r="B4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>36</v>
       </c>
       <c r="D4" s="9" t="s">
@@ -1619,7 +1586,7 @@
       <c r="B7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D7" s="9" t="s">
@@ -1648,7 +1615,7 @@
       <c r="B8" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="9" t="s">
@@ -1690,7 +1657,7 @@
         <v>37</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>96</v>
@@ -1714,10 +1681,14 @@
         <v>85</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="L9" s="12"/>
-      <c r="M9" s="3"/>
+        <v>99</v>
+      </c>
+      <c r="L9" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="10" ht="43.2" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
@@ -1727,10 +1698,10 @@
         <v>37</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>0</v>
@@ -1751,8 +1722,12 @@
       <c r="K10" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="L10" s="12"/>
-      <c r="M10" s="3"/>
+      <c r="L10" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="11" ht="43.2" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
@@ -1762,10 +1737,10 @@
         <v>37</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>80</v>
@@ -1774,7 +1749,7 @@
         <v>87</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>28</v>
@@ -1783,157 +1758,23 @@
         <v>85</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K11" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="L11" s="12"/>
-      <c r="M11" s="3"/>
-    </row>
-    <row r="12" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="9">
-        <v>11</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="K12" s="9"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="9">
-        <v>12</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="9">
-        <v>13</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K14" s="9"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="9">
-        <v>14</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="K15" s="9"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" ht="14.4" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C16" s="9"/>
-    </row>
-    <row r="17" ht="14.4" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C17" s="9"/>
+      <c r="L11" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" ht="14.4" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C12" s="9"/>
+    </row>
+    <row r="13" ht="14.4" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C13" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasheet.xlsx
+++ b/datasheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="login" state="visible" r:id="rId4"/>

--- a/datasheet.xlsx
+++ b/datasheet.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D55479-372B-4B49-A6A8-FC9C0C95F53F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="login" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="userCreation" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="AdminUserManagementUser" state="visible" r:id="rId6"/>
+    <sheet name="login" sheetId="1" r:id="rId1"/>
+    <sheet name="userCreation" sheetId="2" r:id="rId2"/>
+    <sheet name="AdminUserManagementUser" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="104">
   <si>
     <t>Admin</t>
   </si>
@@ -333,51 +334,51 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -732,80 +733,98 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.109375" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>0</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
       </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="11.88671875" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
@@ -873,7 +892,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -921,7 +940,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -961,7 +980,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -999,7 +1018,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1037,7 +1056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1085,7 +1104,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1133,7 +1152,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1181,7 +1200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -1231,7 +1250,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -1275,7 +1294,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -1320,23 +1339,23 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" ht="14.4" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E13" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K7" r:id="rId1"/>
-    <hyperlink ref="L7" r:id="rId2"/>
+    <hyperlink ref="K7" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="L7" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="13.77734375" customWidth="1"/>
     <col min="5" max="5" width="8.5546875" customWidth="1"/>
@@ -1349,7 +1368,7 @@
     <col min="12" max="12" width="32.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" customHeight="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="1" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>9</v>
       </c>
@@ -1390,7 +1409,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -1427,7 +1446,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -1460,7 +1479,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -1497,7 +1516,7 @@
       <c r="L4" s="12"/>
       <c r="M4" s="3"/>
     </row>
-    <row r="5" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -1538,7 +1557,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -1579,7 +1598,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -1608,7 +1627,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" ht="43.2" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -1649,7 +1668,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" ht="72" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -1690,7 +1709,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" ht="43.2" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>9</v>
       </c>
@@ -1729,7 +1748,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" ht="43.2" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>10</v>
       </c>
@@ -1770,14 +1789,14 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" ht="14.4" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="9"/>
     </row>
-    <row r="13" ht="14.4" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/datasheet.xlsx
+++ b/datasheet.xlsx
@@ -1,54 +1,65 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D55479-372B-4B49-A6A8-FC9C0C95F53F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
-    <sheet name="login" sheetId="1" r:id="rId1"/>
-    <sheet name="userCreation" sheetId="2" r:id="rId2"/>
-    <sheet name="AdminUserManagementUser" sheetId="3" r:id="rId3"/>
+    <sheet sheetId="1" name="login" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="userCreation" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="AdminUserManagementUser" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="106">
+  <si>
+    <t>S.No</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>Test case status</t>
+  </si>
   <si>
     <t>Admin</t>
   </si>
   <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Expected Result</t>
-  </si>
-  <si>
-    <t>Actual Result</t>
-  </si>
-  <si>
     <t>admin123</t>
   </si>
   <si>
     <t>PASS</t>
   </si>
   <si>
+    <t xml:space="preserve">test case passed </t>
+  </si>
+  <si>
     <t>Admon</t>
   </si>
   <si>
     <t>FAIL</t>
   </si>
   <si>
+    <t>test case failed</t>
+  </si>
+  <si>
     <t>admin1234</t>
   </si>
   <si>
-    <t>S.No</t>
-  </si>
-  <si>
     <t>ScenarioType</t>
   </si>
   <si>
@@ -70,9 +81,6 @@
     <t>ToggleOn</t>
   </si>
   <si>
-    <t>Username</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -80,9 +88,6 @@
   </si>
   <si>
     <t>Upload image</t>
-  </si>
-  <si>
-    <t>Test case status</t>
   </si>
   <si>
     <t>Positive</t>
@@ -334,51 +339,51 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FF1F1F1F"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color rgb="FF1F1F1F"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -424,7 +429,6 @@
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -435,6 +439,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
@@ -733,35 +738,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="2" t="s">
+    <row r="1" ht="14.4" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>21</v>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -769,16 +774,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -786,16 +794,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -803,28 +814,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="2" max="3" width="11.88671875" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
@@ -842,520 +856,520 @@
     <col min="16" max="16" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="O4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="P7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O9" t="s">
+        <v>34</v>
+      </c>
+      <c r="P9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O10" t="s">
+        <v>34</v>
+      </c>
+      <c r="P10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" ht="14.4" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2" s="3" t="s">
+      <c r="B11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="K11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="O2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="P2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="P3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O4" t="s">
-        <v>38</v>
-      </c>
-      <c r="P4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="P6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="P7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="P8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+      <c r="M11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="O11" t="s">
+        <v>70</v>
+      </c>
+      <c r="P11" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O9" t="s">
-        <v>32</v>
-      </c>
-      <c r="P9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O10" t="s">
-        <v>32</v>
-      </c>
-      <c r="P10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="O11" t="s">
-        <v>68</v>
-      </c>
-      <c r="P11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E13" s="3"/>
+    </row>
+    <row r="13" ht="14.4" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E13" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K7" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="L7" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="K7" r:id="rId1"/>
+    <hyperlink ref="L7" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="13.77734375" customWidth="1"/>
     <col min="5" max="5" width="8.5546875" customWidth="1"/>
@@ -1368,248 +1382,248 @@
     <col min="12" max="12" width="32.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28.8" customHeight="1" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
       <c r="K2" s="11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L2" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
       <c r="H3" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
       <c r="K3" s="11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>80</v>
-      </c>
       <c r="F4" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L4" s="12"/>
-      <c r="M4" s="3"/>
-    </row>
-    <row r="5" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E5" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="M5" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="F6" s="9" t="s">
+      <c r="G6" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>85</v>
-      </c>
       <c r="J6" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" ht="28.8" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -1618,185 +1632,185 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" ht="43.2" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E8" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="L8" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" ht="72" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" ht="43.2" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G10" s="9"/>
       <c r="H10" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" ht="43.2" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E11" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="M11" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" ht="14.4" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C12" s="9"/>
     </row>
-    <row r="13" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" ht="14.4" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C13" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/datasheet.xlsx
+++ b/datasheet.xlsx
@@ -45,7 +45,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t xml:space="preserve">test case passed </t>
+    <t>Login Successful</t>
   </si>
   <si>
     <t>Admon</t>
@@ -54,7 +54,7 @@
     <t>FAIL</t>
   </si>
   <si>
-    <t>test case failed</t>
+    <t>Invalid credentials</t>
   </si>
   <si>
     <t>admin1234</t>
@@ -783,10 +783,10 @@
         <v>8</v>
       </c>
       <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
         <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -803,10 +803,10 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -823,10 +823,10 @@
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
